--- a/data/compliance.xlsx
+++ b/data/compliance.xlsx
@@ -472,11 +472,11 @@
         <v>12</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>45911</v>
+        <v>46117</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>M. Quaye</t>
+          <t>Y. Darko</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46114</v>
+        <v>46142</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -528,11 +528,11 @@
         <v>12</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46139</v>
+        <v>45996</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Y. Darko</t>
+          <t>J. Boateng</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
         <v>12</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>45993</v>
+        <v>45780</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -584,11 +584,11 @@
         <v>3</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46045</v>
+        <v>46150</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>J. Boateng</t>
+          <t>E. Asante</t>
         </is>
       </c>
     </row>
@@ -612,11 +612,11 @@
         <v>12</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46132</v>
+        <v>45869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>E. Asante</t>
+          <t>K. Mensah</t>
         </is>
       </c>
     </row>
@@ -640,11 +640,11 @@
         <v>12</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>45866</v>
+        <v>45969</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>K. Mensah</t>
+          <t>P. Annan</t>
         </is>
       </c>
     </row>
@@ -668,11 +668,11 @@
         <v>36</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>45611</v>
+        <v>45204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>P. Annan</t>
+          <t>K. Mensah</t>
         </is>
       </c>
     </row>
@@ -696,11 +696,11 @@
         <v>12</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>45825</v>
+        <v>46150</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>K. Mensah</t>
+          <t>Y. Darko</t>
         </is>
       </c>
     </row>
@@ -724,11 +724,11 @@
         <v>12</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46147</v>
+        <v>46088</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Y. Darko</t>
+          <t>M. Quaye</t>
         </is>
       </c>
     </row>
@@ -752,11 +752,11 @@
         <v>12</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46085</v>
+        <v>46051</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>M. Quaye</t>
+          <t>Y. Darko</t>
         </is>
       </c>
     </row>
@@ -780,11 +780,11 @@
         <v>12</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46048</v>
+        <v>46142</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Y. Darko</t>
+          <t>S. Addo</t>
         </is>
       </c>
     </row>
@@ -808,11 +808,11 @@
         <v>12</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46139</v>
+        <v>45960</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>S. Addo</t>
+          <t>K. Mensah</t>
         </is>
       </c>
     </row>
